--- a/output/yearly_total_coral_cover_iteration_72_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_72_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.275895451674321</v>
+        <v>1.259912599049183</v>
       </c>
       <c r="C3" t="n">
-        <v>4.626522271988312</v>
+        <v>4.610107450373306</v>
       </c>
       <c r="D3" t="n">
-        <v>6.058880594386436</v>
+        <v>6.061894559838475</v>
       </c>
       <c r="E3" t="n">
-        <v>11.96129831804907</v>
+        <v>11.93191460926096</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.434357353619878</v>
+        <v>1.38839697756189</v>
       </c>
       <c r="C4" t="n">
-        <v>5.160020419606886</v>
+        <v>5.063599970993529</v>
       </c>
       <c r="D4" t="n">
-        <v>6.379166668794742</v>
+        <v>6.255673219366341</v>
       </c>
       <c r="E4" t="n">
-        <v>12.97354444202151</v>
+        <v>12.70767016792176</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.644381399473126</v>
+        <v>1.575548604548733</v>
       </c>
       <c r="C5" t="n">
-        <v>5.836247392642568</v>
+        <v>5.626428998086435</v>
       </c>
       <c r="D5" t="n">
-        <v>6.769315383238559</v>
+        <v>6.573743488015901</v>
       </c>
       <c r="E5" t="n">
-        <v>14.24994417535425</v>
+        <v>13.77572109065107</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.889614900086563</v>
+        <v>1.792742964936989</v>
       </c>
       <c r="C6" t="n">
-        <v>6.65870791339625</v>
+        <v>6.301438190360662</v>
       </c>
       <c r="D6" t="n">
-        <v>7.14598100679497</v>
+        <v>6.89361923861448</v>
       </c>
       <c r="E6" t="n">
-        <v>15.69430382027778</v>
+        <v>14.98780039391213</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.167912433622287</v>
+        <v>2.034879765365475</v>
       </c>
       <c r="C7" t="n">
-        <v>7.633211056580181</v>
+        <v>7.096036722595389</v>
       </c>
       <c r="D7" t="n">
-        <v>7.605019406371333</v>
+        <v>7.250866066125617</v>
       </c>
       <c r="E7" t="n">
-        <v>17.4061428965738</v>
+        <v>16.38178255408648</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.388079096980469</v>
+        <v>1.260864476574424</v>
       </c>
       <c r="C8" t="n">
-        <v>5.286677253197716</v>
+        <v>4.736011884122465</v>
       </c>
       <c r="D8" t="n">
-        <v>5.915847074559419</v>
+        <v>5.555687685278517</v>
       </c>
       <c r="E8" t="n">
-        <v>12.5906034247376</v>
+        <v>11.55256404597541</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.783239720381157</v>
+        <v>1.583877449261766</v>
       </c>
       <c r="C9" t="n">
-        <v>6.505857258140719</v>
+        <v>5.751307211539319</v>
       </c>
       <c r="D9" t="n">
-        <v>6.466450407029559</v>
+        <v>6.096875394902401</v>
       </c>
       <c r="E9" t="n">
-        <v>14.75554738555143</v>
+        <v>13.43206005570349</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.206622256988181</v>
+        <v>1.934750585043402</v>
       </c>
       <c r="C10" t="n">
-        <v>7.897554994928544</v>
+        <v>6.922219734759717</v>
       </c>
       <c r="D10" t="n">
-        <v>7.052334174101989</v>
+        <v>6.665733866946526</v>
       </c>
       <c r="E10" t="n">
-        <v>17.15651142601871</v>
+        <v>15.52270418674964</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.633105858264653</v>
+        <v>2.30635818221041</v>
       </c>
       <c r="C11" t="n">
-        <v>9.384301917522423</v>
+        <v>8.202918741496466</v>
       </c>
       <c r="D11" t="n">
-        <v>7.616653554562312</v>
+        <v>7.221053108325684</v>
       </c>
       <c r="E11" t="n">
-        <v>19.63406133034939</v>
+        <v>17.73033003203256</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.047204818747923</v>
+        <v>2.698485561256284</v>
       </c>
       <c r="C12" t="n">
-        <v>10.9252929468684</v>
+        <v>9.548159834044061</v>
       </c>
       <c r="D12" t="n">
-        <v>8.119230973386747</v>
+        <v>7.812309907032807</v>
       </c>
       <c r="E12" t="n">
-        <v>22.09172873900307</v>
+        <v>20.05895530233315</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.438457448417014</v>
+        <v>3.072394740910748</v>
       </c>
       <c r="C13" t="n">
-        <v>12.48375061441499</v>
+        <v>10.94940282768238</v>
       </c>
       <c r="D13" t="n">
-        <v>8.615115899144287</v>
+        <v>8.335648095824705</v>
       </c>
       <c r="E13" t="n">
-        <v>24.53732396197629</v>
+        <v>22.35744566441783</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.951665348657447</v>
+        <v>1.778504688582394</v>
       </c>
       <c r="C14" t="n">
-        <v>8.718979901232261</v>
+        <v>7.70655258122774</v>
       </c>
       <c r="D14" t="n">
-        <v>6.529417448881729</v>
+        <v>6.391609523636604</v>
       </c>
       <c r="E14" t="n">
-        <v>17.20006269877144</v>
+        <v>15.87666679344674</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.021173086118121</v>
+        <v>1.838911624824701</v>
       </c>
       <c r="C15" t="n">
-        <v>9.398663471836414</v>
+        <v>8.255182650791985</v>
       </c>
       <c r="D15" t="n">
-        <v>6.567087108293679</v>
+        <v>6.449787892590271</v>
       </c>
       <c r="E15" t="n">
-        <v>17.98692366624821</v>
+        <v>16.54388216820696</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.355585806615712</v>
+        <v>2.157577112146173</v>
       </c>
       <c r="C16" t="n">
-        <v>11.06734986222176</v>
+        <v>9.715964329848983</v>
       </c>
       <c r="D16" t="n">
-        <v>7.035861819594489</v>
+        <v>6.977251481650955</v>
       </c>
       <c r="E16" t="n">
-        <v>20.45879748843196</v>
+        <v>18.85079292364611</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.900477023358018</v>
+        <v>1.742219293433432</v>
       </c>
       <c r="C17" t="n">
-        <v>10.15536514983873</v>
+        <v>8.964642629265942</v>
       </c>
       <c r="D17" t="n">
-        <v>6.537565954826977</v>
+        <v>6.529378178973559</v>
       </c>
       <c r="E17" t="n">
-        <v>18.59340812802373</v>
+        <v>17.23624010167293</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.174698792108237</v>
+        <v>2.012769325769769</v>
       </c>
       <c r="C18" t="n">
-        <v>11.81661971010293</v>
+        <v>10.42676930267776</v>
       </c>
       <c r="D18" t="n">
-        <v>6.933475351518589</v>
+        <v>7.042547521460408</v>
       </c>
       <c r="E18" t="n">
-        <v>20.92479385372975</v>
+        <v>19.48208614990794</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.187913116207399</v>
+        <v>2.043664926022416</v>
       </c>
       <c r="C19" t="n">
-        <v>12.61275819338484</v>
+        <v>11.11201938276499</v>
       </c>
       <c r="D19" t="n">
-        <v>7.014675704136843</v>
+        <v>7.183968278257163</v>
       </c>
       <c r="E19" t="n">
-        <v>21.81534701372908</v>
+        <v>20.33965258704457</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.438720202211332</v>
+        <v>2.298938964080671</v>
       </c>
       <c r="C20" t="n">
-        <v>14.4273421100983</v>
+        <v>12.76607773235706</v>
       </c>
       <c r="D20" t="n">
-        <v>7.482517755118618</v>
+        <v>7.724940715728282</v>
       </c>
       <c r="E20" t="n">
-        <v>24.34858006742825</v>
+        <v>22.78995741216601</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.448048411332918</v>
+        <v>1.382654196753038</v>
       </c>
       <c r="C21" t="n">
-        <v>10.55531934707184</v>
+        <v>9.395394251981273</v>
       </c>
       <c r="D21" t="n">
-        <v>6.240273115026959</v>
+        <v>6.479574117937119</v>
       </c>
       <c r="E21" t="n">
-        <v>18.24364087343172</v>
+        <v>17.25762256667143</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_72_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_72_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.259912599049183</v>
+        <v>1.289276672883205</v>
       </c>
       <c r="C3" t="n">
-        <v>4.610107450373306</v>
+        <v>4.608575923954681</v>
       </c>
       <c r="D3" t="n">
-        <v>6.061894559838475</v>
+        <v>6.052754488711936</v>
       </c>
       <c r="E3" t="n">
-        <v>11.93191460926096</v>
+        <v>11.95060708554982</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.38839697756189</v>
+        <v>1.462211373217205</v>
       </c>
       <c r="C4" t="n">
-        <v>5.063599970993529</v>
+        <v>5.068432977228788</v>
       </c>
       <c r="D4" t="n">
-        <v>6.255673219366341</v>
+        <v>6.278498475345726</v>
       </c>
       <c r="E4" t="n">
-        <v>12.70767016792176</v>
+        <v>12.80914282579172</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.575548604548733</v>
+        <v>1.687454580770213</v>
       </c>
       <c r="C5" t="n">
-        <v>5.626428998086435</v>
+        <v>5.617975018017156</v>
       </c>
       <c r="D5" t="n">
-        <v>6.573743488015901</v>
+        <v>6.496789244106573</v>
       </c>
       <c r="E5" t="n">
-        <v>13.77572109065107</v>
+        <v>13.80221884289394</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.792742964936989</v>
+        <v>1.936470152899751</v>
       </c>
       <c r="C6" t="n">
-        <v>6.301438190360662</v>
+        <v>6.27002501283097</v>
       </c>
       <c r="D6" t="n">
-        <v>6.89361923861448</v>
+        <v>6.754408193118295</v>
       </c>
       <c r="E6" t="n">
-        <v>14.98780039391213</v>
+        <v>14.96090335884902</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.034879765365475</v>
+        <v>2.223525232341997</v>
       </c>
       <c r="C7" t="n">
-        <v>7.096036722595389</v>
+        <v>7.013473572630646</v>
       </c>
       <c r="D7" t="n">
-        <v>7.250866066125617</v>
+        <v>7.129560925141875</v>
       </c>
       <c r="E7" t="n">
-        <v>16.38178255408648</v>
+        <v>16.36655973011452</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.260864476574424</v>
+        <v>1.411239338568554</v>
       </c>
       <c r="C8" t="n">
-        <v>4.736011884122465</v>
+        <v>4.608512779312549</v>
       </c>
       <c r="D8" t="n">
-        <v>5.555687685278517</v>
+        <v>5.3362699523496</v>
       </c>
       <c r="E8" t="n">
-        <v>11.55256404597541</v>
+        <v>11.3560220702307</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.583877449261766</v>
+        <v>1.80124532792561</v>
       </c>
       <c r="C9" t="n">
-        <v>5.751307211539319</v>
+        <v>5.563662553081954</v>
       </c>
       <c r="D9" t="n">
-        <v>6.096875394902401</v>
+        <v>5.756295301170749</v>
       </c>
       <c r="E9" t="n">
-        <v>13.43206005570349</v>
+        <v>13.12120318217831</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.934750585043402</v>
+        <v>2.230794156638437</v>
       </c>
       <c r="C10" t="n">
-        <v>6.922219734759717</v>
+        <v>6.697395588965444</v>
       </c>
       <c r="D10" t="n">
-        <v>6.665733866946526</v>
+        <v>6.162948966550017</v>
       </c>
       <c r="E10" t="n">
-        <v>15.52270418674964</v>
+        <v>15.0911387121539</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.30635818221041</v>
+        <v>2.707378036691302</v>
       </c>
       <c r="C11" t="n">
-        <v>8.202918741496466</v>
+        <v>7.998836336726835</v>
       </c>
       <c r="D11" t="n">
-        <v>7.221053108325684</v>
+        <v>6.57049298838796</v>
       </c>
       <c r="E11" t="n">
-        <v>17.73033003203256</v>
+        <v>17.2767073618061</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.698485561256284</v>
+        <v>3.208468188252265</v>
       </c>
       <c r="C12" t="n">
-        <v>9.548159834044061</v>
+        <v>9.428313239937623</v>
       </c>
       <c r="D12" t="n">
-        <v>7.812309907032807</v>
+        <v>7.064554451931835</v>
       </c>
       <c r="E12" t="n">
-        <v>20.05895530233315</v>
+        <v>19.70133588012172</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.072394740910748</v>
+        <v>3.726585998976335</v>
       </c>
       <c r="C13" t="n">
-        <v>10.94940282768238</v>
+        <v>10.95708046716286</v>
       </c>
       <c r="D13" t="n">
-        <v>8.335648095824705</v>
+        <v>7.471668536665059</v>
       </c>
       <c r="E13" t="n">
-        <v>22.35744566441783</v>
+        <v>22.15533500280426</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.778504688582394</v>
+        <v>2.15776364420998</v>
       </c>
       <c r="C14" t="n">
-        <v>7.70655258122774</v>
+        <v>7.793339078283157</v>
       </c>
       <c r="D14" t="n">
-        <v>6.391609523636604</v>
+        <v>5.705367878368084</v>
       </c>
       <c r="E14" t="n">
-        <v>15.87666679344674</v>
+        <v>15.65647060086122</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.838911624824701</v>
+        <v>2.294383654732966</v>
       </c>
       <c r="C15" t="n">
-        <v>8.255182650791985</v>
+        <v>8.50588174454845</v>
       </c>
       <c r="D15" t="n">
-        <v>6.449787892590271</v>
+        <v>5.684545009561009</v>
       </c>
       <c r="E15" t="n">
-        <v>16.54388216820696</v>
+        <v>16.48481040884242</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.157577112146173</v>
+        <v>2.734344070914132</v>
       </c>
       <c r="C16" t="n">
-        <v>9.715964329848983</v>
+        <v>10.16633127169517</v>
       </c>
       <c r="D16" t="n">
-        <v>6.977251481650955</v>
+        <v>6.135834794249182</v>
       </c>
       <c r="E16" t="n">
-        <v>18.85079292364611</v>
+        <v>19.03651013685848</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.742219293433432</v>
+        <v>2.23608747605479</v>
       </c>
       <c r="C17" t="n">
-        <v>8.964642629265942</v>
+        <v>9.522471674818981</v>
       </c>
       <c r="D17" t="n">
-        <v>6.529378178973559</v>
+        <v>5.677132814393945</v>
       </c>
       <c r="E17" t="n">
-        <v>17.23624010167293</v>
+        <v>17.43569196526771</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.012769325769769</v>
+        <v>2.587641511468531</v>
       </c>
       <c r="C18" t="n">
-        <v>10.42676930267776</v>
+        <v>11.21603555202994</v>
       </c>
       <c r="D18" t="n">
-        <v>7.042547521460408</v>
+        <v>6.031180488976474</v>
       </c>
       <c r="E18" t="n">
-        <v>19.48208614990794</v>
+        <v>19.83485755247495</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.043664926022416</v>
+        <v>2.630308266695097</v>
       </c>
       <c r="C19" t="n">
-        <v>11.11201938276499</v>
+        <v>12.08889761839874</v>
       </c>
       <c r="D19" t="n">
-        <v>7.183968278257163</v>
+        <v>6.099618121439518</v>
       </c>
       <c r="E19" t="n">
-        <v>20.33965258704457</v>
+        <v>20.81882400653335</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.298938964080671</v>
+        <v>2.965732187328063</v>
       </c>
       <c r="C20" t="n">
-        <v>12.76607773235706</v>
+        <v>13.9846229828682</v>
       </c>
       <c r="D20" t="n">
-        <v>7.724940715728282</v>
+        <v>6.472701884007392</v>
       </c>
       <c r="E20" t="n">
-        <v>22.78995741216601</v>
+        <v>23.42305705420366</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.382654196753038</v>
+        <v>1.775922692120226</v>
       </c>
       <c r="C21" t="n">
-        <v>9.395394251981273</v>
+        <v>10.33125506853159</v>
       </c>
       <c r="D21" t="n">
-        <v>6.479574117937119</v>
+        <v>5.373399709654068</v>
       </c>
       <c r="E21" t="n">
-        <v>17.25762256667143</v>
+        <v>17.48057747030588</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_72_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_72_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.289276672883205</v>
+        <v>2.648195231750003</v>
       </c>
       <c r="C3" t="n">
-        <v>4.608575923954681</v>
+        <v>7.76738865581642</v>
       </c>
       <c r="D3" t="n">
-        <v>6.052754488711936</v>
+        <v>8.194361185571317</v>
       </c>
       <c r="E3" t="n">
-        <v>11.95060708554982</v>
+        <v>18.60994507313774</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.462211373217205</v>
+        <v>1.196620568188043</v>
       </c>
       <c r="C4" t="n">
-        <v>5.068432977228788</v>
+        <v>4.68246223759138</v>
       </c>
       <c r="D4" t="n">
-        <v>6.278498475345726</v>
+        <v>5.781511425405179</v>
       </c>
       <c r="E4" t="n">
-        <v>12.80914282579172</v>
+        <v>11.6605942311846</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.687454580770213</v>
+        <v>1.396554402264777</v>
       </c>
       <c r="C5" t="n">
-        <v>5.617975018017156</v>
+        <v>5.547472485097072</v>
       </c>
       <c r="D5" t="n">
-        <v>6.496789244106573</v>
+        <v>6.085004360232433</v>
       </c>
       <c r="E5" t="n">
-        <v>13.80221884289394</v>
+        <v>13.02903124759428</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.936470152899751</v>
+        <v>1.620277105530836</v>
       </c>
       <c r="C6" t="n">
-        <v>6.27002501283097</v>
+        <v>6.650995719912932</v>
       </c>
       <c r="D6" t="n">
-        <v>6.754408193118295</v>
+        <v>6.465872308218497</v>
       </c>
       <c r="E6" t="n">
-        <v>14.96090335884902</v>
+        <v>14.73714513366227</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.223525232341997</v>
+        <v>1.853380211587169</v>
       </c>
       <c r="C7" t="n">
-        <v>7.013473572630646</v>
+        <v>7.930516731500123</v>
       </c>
       <c r="D7" t="n">
-        <v>7.129560925141875</v>
+        <v>6.825316223777745</v>
       </c>
       <c r="E7" t="n">
-        <v>16.36655973011452</v>
+        <v>16.60921316686504</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.411239338568554</v>
+        <v>2.084020812118538</v>
       </c>
       <c r="C8" t="n">
-        <v>4.608512779312549</v>
+        <v>9.395708313672447</v>
       </c>
       <c r="D8" t="n">
-        <v>5.3362699523496</v>
+        <v>7.217008056737222</v>
       </c>
       <c r="E8" t="n">
-        <v>11.3560220702307</v>
+        <v>18.69673718252821</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.80124532792561</v>
+        <v>2.292222072919351</v>
       </c>
       <c r="C9" t="n">
-        <v>5.563662553081954</v>
+        <v>10.97439154833357</v>
       </c>
       <c r="D9" t="n">
-        <v>5.756295301170749</v>
+        <v>7.553436724718717</v>
       </c>
       <c r="E9" t="n">
-        <v>13.12120318217831</v>
+        <v>20.82005034597163</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.230794156638437</v>
+        <v>1.360653230700867</v>
       </c>
       <c r="C10" t="n">
-        <v>6.697395588965444</v>
+        <v>7.900035418780701</v>
       </c>
       <c r="D10" t="n">
-        <v>6.162948966550017</v>
+        <v>5.931032405666256</v>
       </c>
       <c r="E10" t="n">
-        <v>15.0911387121539</v>
+        <v>15.19172105514782</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.707378036691302</v>
+        <v>1.324210755919226</v>
       </c>
       <c r="C11" t="n">
-        <v>7.998836336726835</v>
+        <v>8.639330709986719</v>
       </c>
       <c r="D11" t="n">
-        <v>6.57049298838796</v>
+        <v>5.76290811131399</v>
       </c>
       <c r="E11" t="n">
-        <v>17.2767073618061</v>
+        <v>15.72644957721993</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.208468188252265</v>
+        <v>1.463923271710589</v>
       </c>
       <c r="C12" t="n">
-        <v>9.428313239937623</v>
+        <v>10.39353714288901</v>
       </c>
       <c r="D12" t="n">
-        <v>7.064554451931835</v>
+        <v>6.090154073570578</v>
       </c>
       <c r="E12" t="n">
-        <v>19.70133588012172</v>
+        <v>17.94761448817017</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.726585998976335</v>
+        <v>1.167798711678623</v>
       </c>
       <c r="C13" t="n">
-        <v>10.95708046716286</v>
+        <v>10.00175108655523</v>
       </c>
       <c r="D13" t="n">
-        <v>7.471668536665059</v>
+        <v>5.504708465097078</v>
       </c>
       <c r="E13" t="n">
-        <v>22.15533500280426</v>
+        <v>16.67425826333093</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.15776364420998</v>
+        <v>1.278696932350343</v>
       </c>
       <c r="C14" t="n">
-        <v>7.793339078283157</v>
+        <v>11.84159537169896</v>
       </c>
       <c r="D14" t="n">
-        <v>5.705367878368084</v>
+        <v>5.820595606415532</v>
       </c>
       <c r="E14" t="n">
-        <v>15.65647060086122</v>
+        <v>18.94088791046484</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.294383654732966</v>
+        <v>1.242607886742231</v>
       </c>
       <c r="C15" t="n">
-        <v>8.50588174454845</v>
+        <v>12.89700360619542</v>
       </c>
       <c r="D15" t="n">
-        <v>5.684545009561009</v>
+        <v>5.824787669112665</v>
       </c>
       <c r="E15" t="n">
-        <v>16.48481040884242</v>
+        <v>19.96439916205031</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.734344070914132</v>
+        <v>1.362548003770063</v>
       </c>
       <c r="C16" t="n">
-        <v>10.16633127169517</v>
+        <v>15.05069299743277</v>
       </c>
       <c r="D16" t="n">
-        <v>6.135834794249182</v>
+        <v>6.161733298687214</v>
       </c>
       <c r="E16" t="n">
-        <v>19.03651013685848</v>
+        <v>22.57497429989005</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.23608747605479</v>
+        <v>0.8050036650512571</v>
       </c>
       <c r="C17" t="n">
-        <v>9.522471674818981</v>
+        <v>11.21916732720649</v>
       </c>
       <c r="D17" t="n">
-        <v>5.677132814393945</v>
+        <v>5.091284689361704</v>
       </c>
       <c r="E17" t="n">
-        <v>17.43569196526771</v>
+        <v>17.11545568161945</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.587641511468531</v>
+        <v>0.655296957630661</v>
       </c>
       <c r="C18" t="n">
-        <v>11.21603555202994</v>
+        <v>10.22950673646345</v>
       </c>
       <c r="D18" t="n">
-        <v>6.031180488976474</v>
+        <v>4.587402680157029</v>
       </c>
       <c r="E18" t="n">
-        <v>19.83485755247495</v>
+        <v>15.47220637425114</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.630308266695097</v>
+        <v>0.7758555757121695</v>
       </c>
       <c r="C19" t="n">
-        <v>12.08889761839874</v>
+        <v>12.65316692889163</v>
       </c>
       <c r="D19" t="n">
-        <v>6.099618121439518</v>
+        <v>5.036316635400925</v>
       </c>
       <c r="E19" t="n">
-        <v>20.81882400653335</v>
+        <v>18.46533914000473</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.965732187328063</v>
+        <v>0.8934394982498097</v>
       </c>
       <c r="C20" t="n">
-        <v>13.9846229828682</v>
+        <v>15.22574843057702</v>
       </c>
       <c r="D20" t="n">
-        <v>6.472701884007392</v>
+        <v>5.455257833234167</v>
       </c>
       <c r="E20" t="n">
-        <v>23.42305705420366</v>
+        <v>21.574445762061</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.775922692120226</v>
+        <v>0.9918400706464676</v>
       </c>
       <c r="C21" t="n">
-        <v>10.33125506853159</v>
+        <v>17.8143716897498</v>
       </c>
       <c r="D21" t="n">
-        <v>5.373399709654068</v>
+        <v>5.828164881215275</v>
       </c>
       <c r="E21" t="n">
-        <v>17.48057747030588</v>
+        <v>24.63437664161154</v>
       </c>
     </row>
   </sheetData>
